--- a/קטגוריות_ומוצרים.xlsx
+++ b/קטגוריות_ומוצרים.xlsx
@@ -513,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D87"/>
+  <dimension ref="A1:D86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1295,71 +1295,58 @@
       <c r="D64" s="7" t="n"/>
     </row>
     <row r="65" ht="26" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
-        <is>
-          <t>נאצ'וס (חדש)</t>
-        </is>
-      </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>נאצ'וס קטן</t>
+          <t>נאצ'וס</t>
         </is>
       </c>
       <c r="C65" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
+      <c r="D65" s="7" t="n"/>
     </row>
     <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>Sweet - קינוחים</t>
+        </is>
+      </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>נאצ'וס גדול</t>
+          <t>סופלה</t>
         </is>
       </c>
       <c r="C66" s="6" t="n">
-        <v>30</v>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>חדש</t>
-        </is>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="D66" s="7" t="n"/>
     </row>
     <row r="67" ht="26" customHeight="1">
-      <c r="A67" s="4" t="inlineStr">
-        <is>
-          <t>Sweet - קינוחים</t>
-        </is>
-      </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>סופלה</t>
+          <t>תוספת כדור גלידה (פרווה)</t>
         </is>
       </c>
       <c r="C67" s="6" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D67" s="7" t="n"/>
     </row>
     <row r="68" ht="26" customHeight="1">
       <c r="B68" s="5" t="inlineStr">
         <is>
-          <t>תוספת כדור גלידה (פרווה)</t>
+          <t>מלבי</t>
         </is>
       </c>
       <c r="C68" s="6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D68" s="7" t="n"/>
     </row>
     <row r="69" ht="26" customHeight="1">
       <c r="B69" s="5" t="inlineStr">
         <is>
-          <t>מלבי</t>
+          <t>בוואריה</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
@@ -1370,7 +1357,7 @@
     <row r="70" ht="26" customHeight="1">
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>בוואריה</t>
+          <t>מוס שוקולד</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
@@ -1381,29 +1368,34 @@
     <row r="71" ht="26" customHeight="1">
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>מוס שוקולד</t>
+          <t>צ'ורוס</t>
         </is>
       </c>
       <c r="C71" s="6" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="D71" s="7" t="n"/>
     </row>
     <row r="72" ht="26" customHeight="1">
       <c r="B72" s="5" t="inlineStr">
         <is>
-          <t>צ'ורוס</t>
+          <t>אבטיח (בעונה)</t>
         </is>
       </c>
       <c r="C72" s="6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D72" s="7" t="n"/>
     </row>
     <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>נרגילות</t>
+        </is>
+      </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>אבטיח (בעונה)</t>
+          <t>תפוח נחלה</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
@@ -1412,14 +1404,9 @@
       <c r="D73" s="7" t="n"/>
     </row>
     <row r="74" ht="26" customHeight="1">
-      <c r="A74" s="4" t="inlineStr">
-        <is>
-          <t>נרגילות</t>
-        </is>
-      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>תפוח נחלה</t>
+          <t>Love 66</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
@@ -1430,7 +1417,7 @@
     <row r="75" ht="26" customHeight="1">
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>Love 66</t>
+          <t>לימונענע</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
@@ -1441,18 +1428,18 @@
     <row r="76" ht="26" customHeight="1">
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>לימונענע</t>
+          <t>אייס ענבים</t>
         </is>
       </c>
       <c r="C76" s="6" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D76" s="7" t="n"/>
     </row>
     <row r="77" ht="26" customHeight="1">
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>אייס ענבים</t>
+          <t>Love 66 פרימיום</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
@@ -1463,7 +1450,7 @@
     <row r="78" ht="26" customHeight="1">
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>Love 66 פרימיום</t>
+          <t>אייס סוכריה</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
@@ -1474,7 +1461,7 @@
     <row r="79" ht="26" customHeight="1">
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>אייס סוכריה</t>
+          <t>ארטיק אבטיח דובדבן</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
@@ -1485,7 +1472,7 @@
     <row r="80" ht="26" customHeight="1">
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>ארטיק אבטיח דובדבן</t>
+          <t>לידי קילר</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
@@ -1496,7 +1483,7 @@
     <row r="81" ht="26" customHeight="1">
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>לידי קילר</t>
+          <t>אייס פירות יער</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
@@ -1507,7 +1494,7 @@
     <row r="82" ht="26" customHeight="1">
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>אייס פירות יער</t>
+          <t>אייס אבטיח</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
@@ -1518,7 +1505,7 @@
     <row r="83" ht="26" customHeight="1">
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>אייס אבטיח</t>
+          <t>אייס מנגו</t>
         </is>
       </c>
       <c r="C83" s="6" t="n">
@@ -1529,7 +1516,7 @@
     <row r="84" ht="26" customHeight="1">
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>אייס מנגו</t>
+          <t>אייס אוכמניות</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
@@ -1540,48 +1527,36 @@
     <row r="85" ht="26" customHeight="1">
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>אייס אוכמניות</t>
+          <t>מילוי טבק פרימיום</t>
         </is>
       </c>
       <c r="C85" s="6" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D85" s="7" t="n"/>
     </row>
     <row r="86" ht="26" customHeight="1">
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>מילוי טבק פרימיום</t>
+          <t>תוספת ראש קלאוד</t>
         </is>
       </c>
       <c r="C86" s="6" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="D86" s="7" t="n"/>
     </row>
-    <row r="87" ht="26" customHeight="1">
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>תוספת ראש קלאוד</t>
-        </is>
-      </c>
-      <c r="C87" s="6" t="n">
-        <v>25</v>
-      </c>
-      <c r="D87" s="7" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A67:A73"/>
-    <mergeCell ref="A65:A66"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="A4:A6"/>
-    <mergeCell ref="A51:A64"/>
-    <mergeCell ref="A74:A87"/>
+    <mergeCell ref="A66:A72"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="A45:A50"/>
     <mergeCell ref="A7:A18"/>
+    <mergeCell ref="A51:A65"/>
+    <mergeCell ref="A73:A86"/>
     <mergeCell ref="A41:A42"/>
     <mergeCell ref="A37:A40"/>
     <mergeCell ref="A27:A36"/>

--- a/קטגוריות_ומוצרים.xlsx
+++ b/קטגוריות_ומוצרים.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="תפריט הבר" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="תפריט הבר" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -98,7 +98,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -120,11 +120,44 @@
         <color rgb="00333333"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00333333"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00333333"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00333333"/>
+      </left>
+      <right style="thin">
+        <color rgb="00333333"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00333333"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +181,8 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -513,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D86"/>
+  <dimension ref="A1:D87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -575,6 +610,7 @@
       <c r="D4" s="7" t="n"/>
     </row>
     <row r="5" ht="26" customHeight="1">
+      <c r="A5" s="9" t="n"/>
       <c r="B5" s="5" t="inlineStr">
         <is>
           <t>תה</t>
@@ -586,6 +622,7 @@
       <c r="D5" s="7" t="n"/>
     </row>
     <row r="6" ht="26" customHeight="1">
+      <c r="A6" s="10" t="n"/>
       <c r="B6" s="5" t="inlineStr">
         <is>
           <t>אספרסו</t>
@@ -613,6 +650,7 @@
       <c r="D7" s="7" t="n"/>
     </row>
     <row r="8" ht="26" customHeight="1">
+      <c r="A8" s="9" t="n"/>
       <c r="B8" s="5" t="inlineStr">
         <is>
           <t>מים בטעמים</t>
@@ -624,6 +662,7 @@
       <c r="D8" s="7" t="n"/>
     </row>
     <row r="9" ht="26" customHeight="1">
+      <c r="A9" s="9" t="n"/>
       <c r="B9" s="5" t="inlineStr">
         <is>
           <t>סודה</t>
@@ -635,6 +674,7 @@
       <c r="D9" s="7" t="n"/>
     </row>
     <row r="10" ht="26" customHeight="1">
+      <c r="A10" s="9" t="n"/>
       <c r="B10" s="5" t="inlineStr">
         <is>
           <t>קולה</t>
@@ -646,6 +686,7 @@
       <c r="D10" s="7" t="n"/>
     </row>
     <row r="11" ht="26" customHeight="1">
+      <c r="A11" s="9" t="n"/>
       <c r="B11" s="5" t="inlineStr">
         <is>
           <t>קולה זירו</t>
@@ -657,6 +698,7 @@
       <c r="D11" s="7" t="n"/>
     </row>
     <row r="12" ht="26" customHeight="1">
+      <c r="A12" s="9" t="n"/>
       <c r="B12" s="5" t="inlineStr">
         <is>
           <t>ספרייט</t>
@@ -668,6 +710,7 @@
       <c r="D12" s="7" t="n"/>
     </row>
     <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="9" t="n"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
           <t>פיוזטי</t>
@@ -679,6 +722,7 @@
       <c r="D13" s="7" t="n"/>
     </row>
     <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="9" t="n"/>
       <c r="B14" s="5" t="inlineStr">
         <is>
           <t>פאנטה</t>
@@ -690,6 +734,7 @@
       <c r="D14" s="7" t="n"/>
     </row>
     <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="9" t="n"/>
       <c r="B15" s="5" t="inlineStr">
         <is>
           <t>XL</t>
@@ -701,6 +746,7 @@
       <c r="D15" s="7" t="n"/>
     </row>
     <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="9" t="n"/>
       <c r="B16" s="5" t="inlineStr">
         <is>
           <t>לימונדה</t>
@@ -712,6 +758,7 @@
       <c r="D16" s="7" t="n"/>
     </row>
     <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="9" t="n"/>
       <c r="B17" s="5" t="inlineStr">
         <is>
           <t>ברד בטעמים</t>
@@ -723,6 +770,7 @@
       <c r="D17" s="7" t="n"/>
     </row>
     <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="10" t="n"/>
       <c r="B18" s="5" t="inlineStr">
         <is>
           <t>לימונענע גרוס</t>
@@ -750,6 +798,7 @@
       <c r="D19" s="7" t="n"/>
     </row>
     <row r="20" ht="26" customHeight="1">
+      <c r="A20" s="9" t="n"/>
       <c r="B20" s="5" t="inlineStr">
         <is>
           <t>קסטיל</t>
@@ -761,6 +810,7 @@
       <c r="D20" s="7" t="n"/>
     </row>
     <row r="21" ht="26" customHeight="1">
+      <c r="A21" s="9" t="n"/>
       <c r="B21" s="5" t="inlineStr">
         <is>
           <t>קורונה</t>
@@ -772,6 +822,7 @@
       <c r="D21" s="7" t="n"/>
     </row>
     <row r="22" ht="26" customHeight="1">
+      <c r="A22" s="9" t="n"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
           <t>סטלה</t>
@@ -783,6 +834,7 @@
       <c r="D22" s="7" t="n"/>
     </row>
     <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="9" t="n"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
           <t>סטורג' אדום</t>
@@ -794,6 +846,7 @@
       <c r="D23" s="7" t="n"/>
     </row>
     <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="9" t="n"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
           <t>הייניקן</t>
@@ -805,6 +858,7 @@
       <c r="D24" s="7" t="n"/>
     </row>
     <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="9" t="n"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
           <t>קרלסברג</t>
@@ -816,6 +870,7 @@
       <c r="D25" s="7" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="10" t="n"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
           <t>בריזר</t>
@@ -843,6 +898,7 @@
       <c r="D27" s="7" t="n"/>
     </row>
     <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="9" t="n"/>
       <c r="B28" s="5" t="inlineStr">
         <is>
           <t>בקבוק וודקה בלוגה</t>
@@ -854,6 +910,7 @@
       <c r="D28" s="7" t="n"/>
     </row>
     <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="9" t="n"/>
       <c r="B29" s="5" t="inlineStr">
         <is>
           <t>בקבוק ערק + לימונים</t>
@@ -865,6 +922,7 @@
       <c r="D29" s="7" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="9" t="n"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
           <t>בקבוק ויסקי</t>
@@ -876,6 +934,7 @@
       <c r="D30" s="7" t="n"/>
     </row>
     <row r="31" ht="26" customHeight="1">
+      <c r="A31" s="9" t="n"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
           <t>בקבוק יין</t>
@@ -887,6 +946,7 @@
       <c r="D31" s="7" t="n"/>
     </row>
     <row r="32" ht="26" customHeight="1">
+      <c r="A32" s="9" t="n"/>
       <c r="B32" s="5" t="inlineStr">
         <is>
           <t>בלו נאן</t>
@@ -898,6 +958,7 @@
       <c r="D32" s="7" t="n"/>
     </row>
     <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="9" t="n"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
           <t>בקבוק יין אדום</t>
@@ -909,6 +970,7 @@
       <c r="D33" s="7" t="n"/>
     </row>
     <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="9" t="n"/>
       <c r="B34" s="5" t="inlineStr">
         <is>
           <t>כוס וודקה/ערק/ויסקי</t>
@@ -920,6 +982,7 @@
       <c r="D34" s="7" t="n"/>
     </row>
     <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="9" t="n"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
           <t>כוס יין</t>
@@ -931,6 +994,7 @@
       <c r="D35" s="7" t="n"/>
     </row>
     <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="10" t="n"/>
       <c r="B36" s="5" t="inlineStr">
         <is>
           <t>צ'ייסר</t>
@@ -962,6 +1026,7 @@
       </c>
     </row>
     <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="9" t="n"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
           <t>צ'ייסרים - 10 יחידות</t>
@@ -977,6 +1042,7 @@
       </c>
     </row>
     <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="9" t="n"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Apple Pie</t>
@@ -990,6 +1056,7 @@
       </c>
     </row>
     <row r="40" ht="26" customHeight="1">
+      <c r="A40" s="10" t="n"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Honey Bee</t>
@@ -1023,6 +1090,7 @@
       </c>
     </row>
     <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="10" t="n"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Cosmo Lychee</t>
@@ -1045,7 +1113,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>נקניקיה/שניצל בבגט + צ'יפס</t>
+          <t>נקניקיה בבגט + צ'יפס</t>
         </is>
       </c>
       <c r="C43" s="6" t="n">
@@ -1054,25 +1122,20 @@
       <c r="D43" s="7" t="n"/>
     </row>
     <row r="44" ht="26" customHeight="1">
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>שניצל בבגט + צ'יפס</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>שקשוקה</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D44" s="7" t="n"/>
-    </row>
-    <row r="45" ht="26" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>מיקס</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>טבעות &amp; צ'יפס</t>
         </is>
       </c>
       <c r="C45" s="6" t="n">
@@ -1081,9 +1144,14 @@
       <c r="D45" s="7" t="n"/>
     </row>
     <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>מיקס</t>
+        </is>
+      </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>צ'יפס &amp; בטטה</t>
+          <t>טבעות &amp; צ'יפס</t>
         </is>
       </c>
       <c r="C46" s="6" t="n">
@@ -1092,20 +1160,22 @@
       <c r="D46" s="7" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
+      <c r="A47" s="9" t="n"/>
       <c r="B47" s="5" t="inlineStr">
         <is>
+          <t>צ'יפס &amp; בטטה</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D47" s="7" t="n"/>
+    </row>
+    <row r="48" ht="26" customHeight="1">
+      <c r="A48" s="9" t="n"/>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
           <t>נקניקיות &amp; טבעות</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="n">
-        <v>60</v>
-      </c>
-      <c r="D47" s="7" t="n"/>
-    </row>
-    <row r="48" ht="26" customHeight="1">
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>שניצלונים &amp; כדורי פירה</t>
         </is>
       </c>
       <c r="C48" s="6" t="n">
@@ -1114,9 +1184,10 @@
       <c r="D48" s="7" t="n"/>
     </row>
     <row r="49" ht="26" customHeight="1">
+      <c r="A49" s="9" t="n"/>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>שניצלונים &amp; צ'יפס</t>
+          <t>שניצלונים &amp; כדורי פירה</t>
         </is>
       </c>
       <c r="C49" s="6" t="n">
@@ -1125,9 +1196,10 @@
       <c r="D49" s="7" t="n"/>
     </row>
     <row r="50" ht="26" customHeight="1">
+      <c r="A50" s="9" t="n"/>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>נקניקיות &amp; צ'יפס</t>
+          <t>שניצלונים &amp; צ'יפס</t>
         </is>
       </c>
       <c r="C50" s="6" t="n">
@@ -1136,36 +1208,38 @@
       <c r="D50" s="7" t="n"/>
     </row>
     <row r="51" ht="26" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>נקניקיות &amp; צ'יפס</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="n">
+        <v>60</v>
+      </c>
+      <c r="D51" s="7" t="n"/>
+    </row>
+    <row r="52" ht="26" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>נשנושים</t>
         </is>
       </c>
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>צ'יפס</t>
         </is>
       </c>
-      <c r="C51" s="6" t="n">
+      <c r="C52" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D51" s="7" t="n"/>
-    </row>
-    <row r="52" ht="26" customHeight="1">
-      <c r="B52" s="5" t="inlineStr">
+      <c r="D52" s="7" t="n"/>
+    </row>
+    <row r="53" ht="26" customHeight="1">
+      <c r="A53" s="9" t="n"/>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>צ'יפס בטטה</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="n">
-        <v>45</v>
-      </c>
-      <c r="D52" s="7" t="n"/>
-    </row>
-    <row r="53" ht="26" customHeight="1">
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>הומפריז</t>
         </is>
       </c>
       <c r="C53" s="6" t="n">
@@ -1174,9 +1248,10 @@
       <c r="D53" s="7" t="n"/>
     </row>
     <row r="54" ht="26" customHeight="1">
+      <c r="A54" s="9" t="n"/>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>כדורי פירה</t>
+          <t>הומפריז</t>
         </is>
       </c>
       <c r="C54" s="6" t="n">
@@ -1185,20 +1260,22 @@
       <c r="D54" s="7" t="n"/>
     </row>
     <row r="55" ht="26" customHeight="1">
+      <c r="A55" s="9" t="n"/>
       <c r="B55" s="5" t="inlineStr">
         <is>
+          <t>כדורי פירה</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="n">
+        <v>45</v>
+      </c>
+      <c r="D55" s="7" t="n"/>
+    </row>
+    <row r="56" ht="26" customHeight="1">
+      <c r="A56" s="9" t="n"/>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
           <t>שניצלונים</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="n">
-        <v>50</v>
-      </c>
-      <c r="D55" s="7" t="n"/>
-    </row>
-    <row r="56" ht="26" customHeight="1">
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>כרובית מטוגנת</t>
         </is>
       </c>
       <c r="C56" s="6" t="n">
@@ -1207,9 +1284,10 @@
       <c r="D56" s="7" t="n"/>
     </row>
     <row r="57" ht="26" customHeight="1">
+      <c r="A57" s="9" t="n"/>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>פסטלים/סיגרים</t>
+          <t>כרובית מטוגנת</t>
         </is>
       </c>
       <c r="C57" s="6" t="n">
@@ -1218,9 +1296,10 @@
       <c r="D57" s="7" t="n"/>
     </row>
     <row r="58" ht="26" customHeight="1">
+      <c r="A58" s="9" t="n"/>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>נקניקיות מיני</t>
+          <t>פסטלים/סיגרים</t>
         </is>
       </c>
       <c r="C58" s="6" t="n">
@@ -1229,9 +1308,10 @@
       <c r="D58" s="7" t="n"/>
     </row>
     <row r="59" ht="26" customHeight="1">
+      <c r="A59" s="9" t="n"/>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>נקניקיות מרגז</t>
+          <t>נקניקיות מיני</t>
         </is>
       </c>
       <c r="C59" s="6" t="n">
@@ -1240,113 +1320,122 @@
       <c r="D59" s="7" t="n"/>
     </row>
     <row r="60" ht="26" customHeight="1">
+      <c r="A60" s="9" t="n"/>
       <c r="B60" s="5" t="inlineStr">
         <is>
+          <t>נקניקיות מרגז</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D60" s="7" t="n"/>
+    </row>
+    <row r="61" ht="26" customHeight="1">
+      <c r="A61" s="9" t="n"/>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
           <t>טבעות בצל</t>
         </is>
       </c>
-      <c r="C60" s="6" t="n">
+      <c r="C61" s="6" t="n">
         <v>45</v>
       </c>
-      <c r="D60" s="7" t="n"/>
-    </row>
-    <row r="61" ht="26" customHeight="1">
-      <c r="B61" s="5" t="inlineStr">
+      <c r="D61" s="7" t="n"/>
+    </row>
+    <row r="62" ht="26" customHeight="1">
+      <c r="A62" s="9" t="n"/>
+      <c r="B62" s="5" t="inlineStr">
         <is>
           <t>חומוס (עלה/פיתה)</t>
         </is>
       </c>
-      <c r="C61" s="6" t="n">
+      <c r="C62" s="6" t="n">
         <v>40</v>
       </c>
-      <c r="D61" s="7" t="n"/>
-    </row>
-    <row r="62" ht="26" customHeight="1">
-      <c r="B62" s="5" t="inlineStr">
+      <c r="D62" s="7" t="n"/>
+    </row>
+    <row r="63" ht="26" customHeight="1">
+      <c r="A63" s="9" t="n"/>
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>אדממה</t>
         </is>
       </c>
-      <c r="C62" s="6" t="n">
+      <c r="C63" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="D62" s="7" t="n"/>
-    </row>
-    <row r="63" ht="26" customHeight="1">
-      <c r="B63" s="5" t="inlineStr">
+      <c r="D63" s="7" t="n"/>
+    </row>
+    <row r="64" ht="26" customHeight="1">
+      <c r="A64" s="9" t="n"/>
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>פלטה מטוגנים</t>
         </is>
       </c>
-      <c r="C63" s="6" t="n">
+      <c r="C64" s="6" t="n">
         <v>180</v>
       </c>
-      <c r="D63" s="7" t="n"/>
-    </row>
-    <row r="64" ht="26" customHeight="1">
-      <c r="B64" s="5" t="inlineStr">
+      <c r="D64" s="7" t="n"/>
+    </row>
+    <row r="65" ht="26" customHeight="1">
+      <c r="A65" s="9" t="n"/>
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>פלטת ירקות</t>
         </is>
       </c>
-      <c r="C64" s="6" t="n">
+      <c r="C65" s="6" t="n">
         <v>65</v>
       </c>
-      <c r="D64" s="7" t="n"/>
-    </row>
-    <row r="65" ht="26" customHeight="1">
-      <c r="B65" s="5" t="inlineStr">
+      <c r="D65" s="7" t="n"/>
+    </row>
+    <row r="66" ht="26" customHeight="1">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>נאצ'וס</t>
         </is>
       </c>
-      <c r="C65" s="6" t="n">
+      <c r="C66" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="D65" s="7" t="n"/>
-    </row>
-    <row r="66" ht="26" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+      <c r="D66" s="7" t="n"/>
+    </row>
+    <row r="67" ht="26" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>Sweet - קינוחים</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>סופלה</t>
         </is>
       </c>
-      <c r="C66" s="6" t="n">
+      <c r="C67" s="6" t="n">
         <v>35</v>
       </c>
-      <c r="D66" s="7" t="n"/>
-    </row>
-    <row r="67" ht="26" customHeight="1">
-      <c r="B67" s="5" t="inlineStr">
+      <c r="D67" s="7" t="n"/>
+    </row>
+    <row r="68" ht="26" customHeight="1">
+      <c r="A68" s="9" t="n"/>
+      <c r="B68" s="5" t="inlineStr">
         <is>
           <t>תוספת כדור גלידה (פרווה)</t>
         </is>
       </c>
-      <c r="C67" s="6" t="n">
+      <c r="C68" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D67" s="7" t="n"/>
-    </row>
-    <row r="68" ht="26" customHeight="1">
-      <c r="B68" s="5" t="inlineStr">
+      <c r="D68" s="7" t="n"/>
+    </row>
+    <row r="69" ht="26" customHeight="1">
+      <c r="A69" s="9" t="n"/>
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>מלבי</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="D68" s="7" t="n"/>
-    </row>
-    <row r="69" ht="26" customHeight="1">
-      <c r="B69" s="5" t="inlineStr">
-        <is>
-          <t>בוואריה</t>
         </is>
       </c>
       <c r="C69" s="6" t="n">
@@ -1355,9 +1444,10 @@
       <c r="D69" s="7" t="n"/>
     </row>
     <row r="70" ht="26" customHeight="1">
+      <c r="A70" s="9" t="n"/>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>מוס שוקולד</t>
+          <t>בוואריה</t>
         </is>
       </c>
       <c r="C70" s="6" t="n">
@@ -1366,36 +1456,34 @@
       <c r="D70" s="7" t="n"/>
     </row>
     <row r="71" ht="26" customHeight="1">
+      <c r="A71" s="9" t="n"/>
       <c r="B71" s="5" t="inlineStr">
         <is>
+          <t>מוס שוקולד</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="D71" s="7" t="n"/>
+    </row>
+    <row r="72" ht="26" customHeight="1">
+      <c r="A72" s="9" t="n"/>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
           <t>צ'ורוס</t>
         </is>
       </c>
-      <c r="C71" s="6" t="n">
+      <c r="C72" s="6" t="n">
         <v>30</v>
       </c>
-      <c r="D71" s="7" t="n"/>
-    </row>
-    <row r="72" ht="26" customHeight="1">
-      <c r="B72" s="5" t="inlineStr">
+      <c r="D72" s="7" t="n"/>
+    </row>
+    <row r="73" ht="26" customHeight="1">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>אבטיח (בעונה)</t>
-        </is>
-      </c>
-      <c r="C72" s="6" t="n">
-        <v>40</v>
-      </c>
-      <c r="D72" s="7" t="n"/>
-    </row>
-    <row r="73" ht="26" customHeight="1">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>נרגילות</t>
-        </is>
-      </c>
-      <c r="B73" s="5" t="inlineStr">
-        <is>
-          <t>תפוח נחלה</t>
         </is>
       </c>
       <c r="C73" s="6" t="n">
@@ -1404,9 +1492,14 @@
       <c r="D73" s="7" t="n"/>
     </row>
     <row r="74" ht="26" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>נרגילות</t>
+        </is>
+      </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>Love 66</t>
+          <t>תפוח נחלה</t>
         </is>
       </c>
       <c r="C74" s="6" t="n">
@@ -1415,9 +1508,10 @@
       <c r="D74" s="7" t="n"/>
     </row>
     <row r="75" ht="26" customHeight="1">
+      <c r="A75" s="9" t="n"/>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>לימונענע</t>
+          <t>Love 66</t>
         </is>
       </c>
       <c r="C75" s="6" t="n">
@@ -1426,20 +1520,22 @@
       <c r="D75" s="7" t="n"/>
     </row>
     <row r="76" ht="26" customHeight="1">
+      <c r="A76" s="9" t="n"/>
       <c r="B76" s="5" t="inlineStr">
         <is>
+          <t>לימונענע</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="n">
+        <v>40</v>
+      </c>
+      <c r="D76" s="7" t="n"/>
+    </row>
+    <row r="77" ht="26" customHeight="1">
+      <c r="A77" s="9" t="n"/>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
           <t>אייס ענבים</t>
-        </is>
-      </c>
-      <c r="C76" s="6" t="n">
-        <v>90</v>
-      </c>
-      <c r="D76" s="7" t="n"/>
-    </row>
-    <row r="77" ht="26" customHeight="1">
-      <c r="B77" s="5" t="inlineStr">
-        <is>
-          <t>Love 66 פרימיום</t>
         </is>
       </c>
       <c r="C77" s="6" t="n">
@@ -1448,9 +1544,10 @@
       <c r="D77" s="7" t="n"/>
     </row>
     <row r="78" ht="26" customHeight="1">
+      <c r="A78" s="9" t="n"/>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>אייס סוכריה</t>
+          <t>Love 66 פרימיום</t>
         </is>
       </c>
       <c r="C78" s="6" t="n">
@@ -1459,9 +1556,10 @@
       <c r="D78" s="7" t="n"/>
     </row>
     <row r="79" ht="26" customHeight="1">
+      <c r="A79" s="9" t="n"/>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>ארטיק אבטיח דובדבן</t>
+          <t>אייס סוכריה</t>
         </is>
       </c>
       <c r="C79" s="6" t="n">
@@ -1470,9 +1568,10 @@
       <c r="D79" s="7" t="n"/>
     </row>
     <row r="80" ht="26" customHeight="1">
+      <c r="A80" s="9" t="n"/>
       <c r="B80" s="5" t="inlineStr">
         <is>
-          <t>לידי קילר</t>
+          <t>ארטיק אבטיח דובדבן</t>
         </is>
       </c>
       <c r="C80" s="6" t="n">
@@ -1481,9 +1580,10 @@
       <c r="D80" s="7" t="n"/>
     </row>
     <row r="81" ht="26" customHeight="1">
+      <c r="A81" s="9" t="n"/>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>אייס פירות יער</t>
+          <t>לידי קילר</t>
         </is>
       </c>
       <c r="C81" s="6" t="n">
@@ -1492,9 +1592,10 @@
       <c r="D81" s="7" t="n"/>
     </row>
     <row r="82" ht="26" customHeight="1">
+      <c r="A82" s="9" t="n"/>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>אייס אבטיח</t>
+          <t>אייס פירות יער</t>
         </is>
       </c>
       <c r="C82" s="6" t="n">
@@ -1503,9 +1604,10 @@
       <c r="D82" s="7" t="n"/>
     </row>
     <row r="83" ht="26" customHeight="1">
+      <c r="A83" s="9" t="n"/>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>אייס מנגו</t>
+          <t>אייס אבטיח</t>
         </is>
       </c>
       <c r="C83" s="6" t="n">
@@ -1514,9 +1616,10 @@
       <c r="D83" s="7" t="n"/>
     </row>
     <row r="84" ht="26" customHeight="1">
+      <c r="A84" s="9" t="n"/>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>אייס אוכמניות</t>
+          <t>אייס מנגו</t>
         </is>
       </c>
       <c r="C84" s="6" t="n">
@@ -1525,26 +1628,40 @@
       <c r="D84" s="7" t="n"/>
     </row>
     <row r="85" ht="26" customHeight="1">
+      <c r="A85" s="9" t="n"/>
       <c r="B85" s="5" t="inlineStr">
         <is>
+          <t>אייס אוכמניות</t>
+        </is>
+      </c>
+      <c r="C85" s="6" t="n">
+        <v>90</v>
+      </c>
+      <c r="D85" s="7" t="n"/>
+    </row>
+    <row r="86" ht="26" customHeight="1">
+      <c r="A86" s="9" t="n"/>
+      <c r="B86" s="5" t="inlineStr">
+        <is>
           <t>מילוי טבק פרימיום</t>
         </is>
       </c>
-      <c r="C85" s="6" t="n">
+      <c r="C86" s="6" t="n">
         <v>50</v>
       </c>
-      <c r="D85" s="7" t="n"/>
-    </row>
-    <row r="86" ht="26" customHeight="1">
-      <c r="B86" s="5" t="inlineStr">
+      <c r="D86" s="7" t="n"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="10" t="n"/>
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>תוספת ראש קלאוד</t>
         </is>
       </c>
-      <c r="C86" s="6" t="n">
+      <c r="C87" s="6" t="n">
         <v>25</v>
       </c>
-      <c r="D86" s="7" t="n"/>
+      <c r="D87" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
